--- a/practice/answers/s1_q20.xlsx
+++ b/practice/answers/s1_q20.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Answer" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Answer" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,10 +18,10 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="165" formatCode="DD-MMM-YY"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
     <numFmt numFmtId="166" formatCode="0.0"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -30,45 +30,10 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Arial"/>
       <b val="1"/>
-      <color rgb="004A7C59"/>
-      <sz val="13"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <color rgb="005C6B62"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <color rgb="0024302A"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Consolas"/>
-      <color rgb="002F5D46"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="0024302A"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <color rgb="005C6B62"/>
-      <sz val="9"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -77,12 +42,27 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="004A7C59"/>
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F6EFD9"/>
+        <fgColor rgb="00D9EAD3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00CFE2F3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F4CCCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9D2E9"/>
       </patternFill>
     </fill>
   </fills>
@@ -98,31 +78,30 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -488,195 +467,269 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Dates are numbers wearing a format</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="32" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Real dates sit right-aligned and can be subtracted. Format one as General and the serial number underneath is visible.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="18" customHeight="1"/>
-    <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>Tonnes</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>Days since previous</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>The formula in C</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="5" t="n">
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n">
         <v>46261</v>
       </c>
-      <c r="B5" s="6" t="n">
+      <c r="B2" s="5" t="n">
         <v>51.4</v>
       </c>
-    </row>
-    <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="5" t="n">
+      <c r="C2" s="6" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="n">
         <v>46269</v>
       </c>
-      <c r="B6" s="6" t="n">
+      <c r="B3" s="5" t="n">
         <v>46.9</v>
+      </c>
+      <c r="C3" s="7">
+        <f>A3-A2</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="n">
+        <v>46276</v>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>58.3</v>
+      </c>
+      <c r="C4" s="7">
+        <f>A4-A3</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>44.2</v>
+      </c>
+      <c r="C5" s="7">
+        <f>A5-A4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>53.7</v>
       </c>
       <c r="C6" s="7">
         <f>A6-A5</f>
         <v/>
       </c>
-      <c r="D6" s="8">
-        <f>_xlfn.FORMULATEXT(C6)</f>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>Span, first to last (days)</t>
+        </is>
+      </c>
+      <c r="B8" s="9">
+        <f>A6-A2</f>
         <v/>
       </c>
     </row>
-    <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="5" t="n">
-        <v>46276</v>
-      </c>
-      <c r="B7" s="6" t="n">
-        <v>58.3</v>
-      </c>
-      <c r="C7" s="7">
-        <f>A7-A6</f>
+    <row r="9">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>Total tonnes</t>
+        </is>
+      </c>
+      <c r="B9" s="10">
+        <f>SUM(B2:B6)</f>
         <v/>
       </c>
-      <c r="D7" s="8">
-        <f>_xlfn.FORMULATEXT(C7)</f>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>Average tonnes</t>
+        </is>
+      </c>
+      <c r="B10" s="10">
+        <f>AVERAGE(B2:B6)</f>
         <v/>
       </c>
     </row>
-    <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="5" t="n">
-        <v>46290</v>
-      </c>
-      <c r="B8" s="6" t="n">
-        <v>44.2</v>
-      </c>
-      <c r="C8" s="7">
-        <f>A8-A7</f>
+    <row r="11">
+      <c r="A11" s="11" t="inlineStr">
+        <is>
+          <t>First date shown as General</t>
+        </is>
+      </c>
+      <c r="B11" s="11">
+        <f>A2</f>
         <v/>
       </c>
-      <c r="D8" s="8">
-        <f>_xlfn.FORMULATEXT(C8)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="5" t="n">
-        <v>46301</v>
-      </c>
-      <c r="B9" s="6" t="n">
-        <v>53.7</v>
-      </c>
-      <c r="C9" s="7">
-        <f>A9-A8</f>
-        <v/>
-      </c>
-      <c r="D9" s="8">
-        <f>_xlfn.FORMULATEXT(C9)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="18" customHeight="1"/>
-    <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="9" t="inlineStr">
-        <is>
-          <t>Span, first to last</t>
-        </is>
-      </c>
-      <c r="C11" s="7">
-        <f>A9-A5</f>
-        <v/>
-      </c>
-      <c r="D11" s="8">
-        <f>_xlfn.FORMULATEXT(C11)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="9" t="inlineStr">
-        <is>
-          <t>Total tonnes</t>
-        </is>
-      </c>
-      <c r="C12" s="10">
-        <f>SUM(B5:B9)</f>
-        <v/>
-      </c>
-      <c r="D12" s="8">
-        <f>_xlfn.FORMULATEXT(C12)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="9" t="inlineStr">
-        <is>
-          <t>Average load</t>
-        </is>
-      </c>
-      <c r="C13" s="10">
-        <f>AVERAGE(B5:B9)</f>
-        <v/>
-      </c>
-      <c r="D13" s="8">
-        <f>_xlfn.FORMULATEXT(C13)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="18" customHeight="1"/>
-    <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="9" t="inlineStr">
-        <is>
-          <t>The first date as a plain number</t>
-        </is>
-      </c>
-      <c r="C15" s="7">
-        <f>A5</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="18" customHeight="1"/>
-    <row r="17" ht="30" customHeight="1">
-      <c r="A17" s="11" t="inlineStr">
-        <is>
-          <t>46,261 -- days since 30 December 1899. If the dates had arrived as text they would sit left in their cells and the Days column would return #VALUE!, because text cannot be subtracted.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="18" customHeight="1"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="12" t="inlineStr">
+        <is>
+          <t>The dates sit right-aligned in their cells, the default for real dates; text sits left. That alignment is the quickest check before writing any formula.</t>
+        </is>
+      </c>
+      <c r="B13" s="13" t="n"/>
+      <c r="C13" s="13" t="n"/>
+      <c r="D13" s="13" t="n"/>
+      <c r="E13" s="13" t="n"/>
+      <c r="F13" s="13" t="n"/>
+      <c r="G13" s="13" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="13" t="n"/>
+      <c r="B14" s="13" t="n"/>
+      <c r="C14" s="13" t="n"/>
+      <c r="D14" s="13" t="n"/>
+      <c r="E14" s="13" t="n"/>
+      <c r="F14" s="13" t="n"/>
+      <c r="G14" s="13" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="14" t="inlineStr">
+        <is>
+          <t>Shown as General the first date is 46,261 -- the serial number Excel stores for 27 August 2026. A date is a count of days held as an ordinary number, which is why one date can be subtracted from another. (The count runs from 30 December 1899.) The date cell keeps its format; the cell above shows the same value as General.</t>
+        </is>
+      </c>
+      <c r="B16" s="11" t="n"/>
+      <c r="C16" s="11" t="n"/>
+      <c r="D16" s="11" t="n"/>
+      <c r="E16" s="11" t="n"/>
+      <c r="F16" s="11" t="n"/>
+      <c r="G16" s="11" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="11" t="n"/>
+      <c r="B17" s="11" t="n"/>
+      <c r="C17" s="11" t="n"/>
+      <c r="D17" s="11" t="n"/>
+      <c r="E17" s="11" t="n"/>
+      <c r="F17" s="11" t="n"/>
+      <c r="G17" s="11" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="11" t="n"/>
+      <c r="B18" s="11" t="n"/>
+      <c r="C18" s="11" t="n"/>
+      <c r="D18" s="11" t="n"/>
+      <c r="E18" s="11" t="n"/>
+      <c r="F18" s="11" t="n"/>
+      <c r="G18" s="11" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="11" t="n"/>
+      <c r="B19" s="11" t="n"/>
+      <c r="C19" s="11" t="n"/>
+      <c r="D19" s="11" t="n"/>
+      <c r="E19" s="11" t="n"/>
+      <c r="F19" s="11" t="n"/>
+      <c r="G19" s="11" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="15" t="inlineStr">
+        <is>
+          <t>Excel converts date-shaped text when it is used in arithmetic, so subtracting two text dates still returns a sensible day count. The damage shows up in the range functions: COUNT, SUM and AVERAGE skip text entirely, so a column of text dates counts as zero values with no error, and sorting goes alphabetical.</t>
+        </is>
+      </c>
+      <c r="B21" s="16" t="n"/>
+      <c r="C21" s="16" t="n"/>
+      <c r="D21" s="16" t="n"/>
+      <c r="E21" s="16" t="n"/>
+      <c r="F21" s="16" t="n"/>
+      <c r="G21" s="16" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="16" t="n"/>
+      <c r="B22" s="16" t="n"/>
+      <c r="C22" s="16" t="n"/>
+      <c r="D22" s="16" t="n"/>
+      <c r="E22" s="16" t="n"/>
+      <c r="F22" s="16" t="n"/>
+      <c r="G22" s="16" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="16" t="n"/>
+      <c r="B23" s="16" t="n"/>
+      <c r="C23" s="16" t="n"/>
+      <c r="D23" s="16" t="n"/>
+      <c r="E23" s="16" t="n"/>
+      <c r="F23" s="16" t="n"/>
+      <c r="G23" s="16" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="13" t="inlineStr">
+        <is>
+          <t>Part (a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>Part (b)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="8" t="inlineStr">
+        <is>
+          <t>Part (c)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="11" t="inlineStr">
+        <is>
+          <t>Part (d)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="16" t="inlineStr">
+        <is>
+          <t>Part (e)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A17:D17"/>
+  <mergeCells count="3">
+    <mergeCell ref="A16:G19"/>
+    <mergeCell ref="A21:G23"/>
+    <mergeCell ref="A13:G14"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
